--- a/output/pdf_financials_xlsx/TSD.xlsx
+++ b/output/pdf_financials_xlsx/TSD.xlsx
@@ -6442,28 +6442,28 @@
         <v>0</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0</v>
+        <v>-1.909448</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0</v>
+        <v>-3.340515</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0</v>
+        <v>-4.5441</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0</v>
+        <v>-5.666645</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>0</v>
+        <v>-5.480643</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>0</v>
+        <v>-5.106837</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>0</v>
+        <v>-5.7675</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>0</v>
+        <v>-5.651957</v>
       </c>
       <c r="N91" s="3" t="n">
         <v>0</v>
@@ -19770,7 +19770,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
           <t>-</t>
@@ -21630,7 +21634,11 @@
           <t>Foreign translation reserve</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
           <t>-</t>
@@ -51690,7 +51698,7 @@
         <v>-0.927572</v>
       </c>
       <c r="O405" s="5" t="n">
-        <v>1.6761</v>
+        <v>-1.6761</v>
       </c>
       <c r="P405" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/TSD.xlsx
+++ b/output/pdf_financials_xlsx/TSD.xlsx
@@ -1124,10 +1124,10 @@
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.00049</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>2.6e-05</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
@@ -1136,13 +1136,13 @@
         <v>0</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>5.5e-05</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>4.3e-05</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>4e-06</v>
       </c>
       <c r="N12" s="1" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>-0.293095</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.778389</v>
+        <v>0.777899</v>
       </c>
       <c r="H27" s="1" t="inlineStr">
         <is>
@@ -2247,13 +2247,13 @@
         <v>-2.057669</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.927572</v>
+        <v>-0.927627</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-1.6761</v>
+        <v>-1.676143</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.182068</v>
+        <v>-0.182072</v>
       </c>
       <c r="N27" s="1" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>-0.293095</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.778389</v>
+        <v>0.777899</v>
       </c>
       <c r="H29" s="1" t="inlineStr">
         <is>
@@ -2381,13 +2381,13 @@
         <v>-2.057669</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.927572</v>
+        <v>-0.927627</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1.6761</v>
+        <v>-1.676143</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.182068</v>
+        <v>-0.182072</v>
       </c>
       <c r="N29" s="1" t="inlineStr">
         <is>
@@ -2689,40 +2689,40 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.061827</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.108341</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.108341</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.505965</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.982051</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.610622</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.232585</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.07391</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>4.215333</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>1.081209</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.007481</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.005599</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>0</v>
@@ -2734,10 +2734,10 @@
         <v>0</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.040049</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.001856</v>
       </c>
       <c r="S34" s="1" t="inlineStr">
         <is>
@@ -2815,40 +2815,40 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.061827</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.108341</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.108341</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>1.505965</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.982051</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.610622</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.232585</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.07391</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>4.215333</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>1.081209</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.007481</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.005599</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>0</v>
@@ -2860,10 +2860,10 @@
         <v>0</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.040049</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.001856</v>
       </c>
       <c r="S36" s="1" t="inlineStr">
         <is>
@@ -3571,40 +3571,40 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.081318</v>
+        <v>0.019491</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.175981</v>
+        <v>0.06764000000000001</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.175981</v>
+        <v>0.06764000000000001</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.685317</v>
+        <v>0.179352</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.091082</v>
+        <v>0.109031</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.695668</v>
+        <v>0.085046</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.275226</v>
+        <v>0.042641</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.11673</v>
+        <v>0.04282</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>4.315643</v>
+        <v>0.10031</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1.353599</v>
+        <v>0.27239</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.055418</v>
+        <v>0.047937</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.038192</v>
+        <v>0.032593</v>
       </c>
       <c r="N48" s="3" t="n">
         <v>0</v>
@@ -3616,10 +3616,10 @@
         <v>0</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.097816</v>
+        <v>0.057767</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.039349</v>
+        <v>0.037493</v>
       </c>
       <c r="S48" s="1" t="inlineStr">
         <is>
@@ -9828,7 +9828,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -12420,7 +12420,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -18688,7 +18688,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E89" s="5" t="n">
@@ -20916,7 +20916,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -23850,7 +23850,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -49006,7 +49006,7 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">

--- a/output/pdf_financials_xlsx/TSD.xlsx
+++ b/output/pdf_financials_xlsx/TSD.xlsx
@@ -2332,10 +2332,10 @@
         <v>0</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>0</v>
+        <v>0.043042</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>0</v>
+        <v>0.016074</v>
       </c>
       <c r="S28" s="1" t="inlineStr">
         <is>
@@ -2401,10 +2401,10 @@
         <v>-2.019718</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-1.151356</v>
+        <v>-1.108314</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-1.043242</v>
+        <v>-1.027168</v>
       </c>
       <c r="S29" s="1" t="inlineStr">
         <is>
@@ -43066,7 +43066,11 @@
           <t>Amortization expense</t>
         </is>
       </c>
-      <c r="D322" t="inlineStr"/>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E322" t="inlineStr">
         <is>
           <t>-</t>
